--- a/data/trans_camb/P2A_psíq_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 6,25</t>
+          <t>-0,24; 6,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,42</t>
+          <t>-1,67; 3,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,45</t>
+          <t>-3,14; 1,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,54</t>
+          <t>0,26; 5,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,77</t>
+          <t>-0,84; 3,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,17</t>
+          <t>-0,12; 4,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,77</t>
+          <t>0,84; 4,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,7</t>
+          <t>-0,42; 2,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,55</t>
+          <t>-0,66; 2,37</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 1025,35</t>
+          <t>-31,92; 1174,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,64; 604,8</t>
+          <t>-67,83; 573,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-92,38; 428,88</t>
+          <t>-96,18; 317,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,24; —</t>
+          <t>-36,55; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,35; —</t>
+          <t>-55,72; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 778,58</t>
+          <t>25,16; 879,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 459,98</t>
+          <t>-32,09; 498,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,36; 442,06</t>
+          <t>-47,68; 427,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,21</t>
+          <t>-0,48; 2,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,45</t>
+          <t>-1,45; 0,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,37</t>
+          <t>0,49; 4,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,04</t>
+          <t>-3,69; 0,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -0,49</t>
+          <t>-4,27; -0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,21</t>
+          <t>-2,05; 2,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,67</t>
+          <t>-1,71; 0,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; -0,32</t>
+          <t>-2,28; -0,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,54</t>
+          <t>-0,29; 2,73</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-84,16; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,12; —</t>
+          <t>-54,62; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,27; 21,53</t>
+          <t>-84,6; 13,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,92; -13,61</t>
+          <t>-92,43; -16,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 120,1</t>
+          <t>-52,81; 101,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,01; 57,82</t>
+          <t>-70,24; 58,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,92; -9,92</t>
+          <t>-87,76; -7,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 208,44</t>
+          <t>-18,66; 237,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,28</t>
+          <t>0,27; 5,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>-2,01; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,19</t>
+          <t>-0,18; 3,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,71</t>
+          <t>-0,11; 3,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,09</t>
+          <t>-0,73; 2,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,09</t>
+          <t>0,07; 3,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,6</t>
+          <t>0,44; 3,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,81</t>
+          <t>-0,86; 0,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,61</t>
+          <t>0,39; 2,6</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,89; —</t>
+          <t>-62,54; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,52; —</t>
+          <t>-53,16; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 10067377,78</t>
+          <t>-76,54; 9903179,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 5892906,11</t>
+          <t>-100,0; 12206045,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 12364077,83</t>
+          <t>-23,7; 11636253,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 1408,71</t>
+          <t>0,61; 1508,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,2; 414,88</t>
+          <t>-100,0; 385,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,24; 1203,16</t>
+          <t>9,71; 1207,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,48</t>
+          <t>-1,85; 1,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,62</t>
+          <t>-0,37; 3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; -0,02</t>
+          <t>-2,79; -0,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,27</t>
+          <t>0,46; 4,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,2</t>
+          <t>1,28; 6,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,69</t>
+          <t>-0,94; 1,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,34</t>
+          <t>-0,17; 2,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,36</t>
+          <t>1,16; 4,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,7</t>
+          <t>-1,17; 0,76</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,31; 397,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,51; 691,11</t>
+          <t>-43,96; 917,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,42; 1671,13</t>
+          <t>-8,09; 1925,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,79; 2248,31</t>
+          <t>49,26; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,19; 634,1</t>
+          <t>-66,96; 683,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 483,53</t>
+          <t>-23,21; 474,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>46,28; 837,11</t>
+          <t>55,37; 839,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-72,15; 142,47</t>
+          <t>-67,14; 162,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 5,47</t>
+          <t>-0,16; 6,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,39</t>
+          <t>-2,45; 1,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,04</t>
+          <t>-2,61; 0,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,1</t>
+          <t>-0,86; 4,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,99</t>
+          <t>-2,19; 2,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,14</t>
+          <t>-4,04; 0,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,3</t>
+          <t>0,18; 4,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,45</t>
+          <t>-1,61; 1,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,01</t>
+          <t>-2,47; 0,06</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,11; 1197,12</t>
+          <t>-37,73; 1397,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-57,16; —</t>
+          <t>-52,71; 1210,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-87,73; —</t>
+          <t>-85,56; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 575,35</t>
+          <t>-13,01; 683,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-73,9; 210,15</t>
+          <t>-77,01; 248,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-97,42; 32,08</t>
+          <t>-95,82; 42,55</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,01; 3,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,05</t>
+          <t>1,5; 6,02</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,22</t>
+          <t>1,1; 5,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,43</t>
+          <t>0,34; 3,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,83</t>
+          <t>2,27; 5,38</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,5</t>
+          <t>0,93; 3,41</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,65</t>
+          <t>-0,13; 1,71</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,19</t>
+          <t>2,23; 5,04</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,28</t>
+          <t>-0,04; 2,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,56</t>
+          <t>-1,19; 0,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,44</t>
+          <t>1,54; 5,63</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,65</t>
+          <t>-0,47; 1,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,07</t>
+          <t>-0,73; 1,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,46; 59,1</t>
+          <t>4,37; 63,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,62</t>
+          <t>0,03; 1,58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,53</t>
+          <t>-0,67; 0,65</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,61; 49,02</t>
+          <t>3,59; 46,1</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 720,73</t>
+          <t>-26,94; 636,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 277,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>87,64; 1830,23</t>
+          <t>88,89; 1695,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 543,28</t>
+          <t>-52,69; 574,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,32; 331,64</t>
+          <t>-68,35; 390,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>466,82; —</t>
+          <t>443,6; 35553,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 340,2</t>
+          <t>-1,17; 390,11</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 115,44</t>
+          <t>-62,84; 184,29</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>407,29; 12710,45</t>
+          <t>405,99; 17995,41</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,05</t>
+          <t>-1,18; 1,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,84</t>
+          <t>-1,1; 0,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,51</t>
+          <t>-1,02; 1,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,0</t>
+          <t>-0,43; 2,13</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,57</t>
+          <t>-0,91; 1,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,94</t>
+          <t>-0,37; 1,88</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,12</t>
+          <t>-0,5; 1,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,86</t>
+          <t>-0,68; 0,91</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,39</t>
+          <t>-0,42; 1,42</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-80,67; 249,57</t>
+          <t>-77,67; 257,9</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-73,42; 180,15</t>
+          <t>-73,18; 198,98</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,18; 253,28</t>
+          <t>-58,03; 270,97</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 366,28</t>
+          <t>-36,91; 331,33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-58,25; 256,52</t>
+          <t>-58,84; 231,98</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 298,91</t>
+          <t>-31,25; 264,09</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 153,18</t>
+          <t>-35,84; 184,73</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-48,82; 124,8</t>
+          <t>-46,33; 144,79</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 193,99</t>
+          <t>-27,17; 192,26</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,55</t>
+          <t>0,39; 1,6</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,51</t>
+          <t>-0,46; 0,53</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,9</t>
+          <t>0,48; 1,85</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,56</t>
+          <t>0,3; 1,5</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,02</t>
+          <t>-0,1; 1,02</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,48; 24,28</t>
+          <t>1,47; 24,08</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,33</t>
+          <t>0,5; 1,36</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,65</t>
+          <t>-0,11; 0,63</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,26; 14,1</t>
+          <t>1,33; 13,61</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>19,85; 223,93</t>
+          <t>29,43; 224,43</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 71,14</t>
+          <t>-40,69; 76,23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>43,71; 266,99</t>
+          <t>39,36; 266,17</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>20,86; 164,38</t>
+          <t>19,11; 165,38</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 112,24</t>
+          <t>-7,8; 105,94</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>120,21; 2712,32</t>
+          <t>117,93; 2563,93</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>40,07; 154,51</t>
+          <t>40,01; 162,16</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 76,2</t>
+          <t>-10,05; 74,45</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>117,6; 1453,47</t>
+          <t>121,35; 1392,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,69</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 6,05</t>
+          <t>-0,15; 6,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,31</t>
+          <t>-1,75; 3,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,22</t>
+          <t>-2,72; 1,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,36</t>
+          <t>0,41; 5,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,77</t>
+          <t>-0,66; 3,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 4,63</t>
+          <t>-0,18; 3,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,8</t>
+          <t>0,74; 4,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,8</t>
+          <t>-0,65; 2,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,37</t>
+          <t>-0,69; 2,14</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-32,97%</t>
+          <t>-13,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>249,68%</t>
+          <t>200,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 1174,47</t>
+          <t>-31,81; 1234,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-67,83; 573,37</t>
+          <t>-77,72; 560,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-96,18; 317,9</t>
+          <t>-86,39; 304,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,55; —</t>
+          <t>-34,06; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,72; —</t>
+          <t>-64,0; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,16; 879,13</t>
+          <t>24,57; 862,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 498,35</t>
+          <t>-41,96; 394,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 427,35</t>
+          <t>-47,02; 390,71</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,37</t>
+          <t>-0,59; 2,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,45</t>
+          <t>-1,69; 0,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,39</t>
+          <t>0,5; 4,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,11</t>
+          <t>-3,5; 0,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; -0,61</t>
+          <t>-4,04; -0,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,11</t>
+          <t>-1,8; 2,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,64</t>
+          <t>-1,61; 0,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,23</t>
+          <t>-2,22; -0,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,73</t>
+          <t>-0,21; 2,67</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>375,75%</t>
+          <t>373,89%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-84,16; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,62; —</t>
+          <t>-41,19; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,6; 13,02</t>
+          <t>-83,78; 16,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-92,43; -16,29</t>
+          <t>-91,08; -4,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 101,15</t>
+          <t>-44,24; 141,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,24; 58,75</t>
+          <t>-66,32; 60,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,76; -7,66</t>
+          <t>-88,13; -17,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 237,56</t>
+          <t>-12,22; 207,36</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,35</t>
+          <t>0,03; 5,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,0</t>
+          <t>-2,08; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,08</t>
+          <t>0,08; 4,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,62</t>
+          <t>-0,18; 3,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,2</t>
+          <t>-0,89; 2,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,12</t>
+          <t>-0,13; 3,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,55</t>
+          <t>0,38; 3,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,83</t>
+          <t>-0,96; 0,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,6</t>
+          <t>0,57; 2,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>213,48%</t>
+          <t>277,0%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>252,7%</t>
+          <t>243,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>233,64%</t>
+          <t>259,27%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,54; —</t>
+          <t>-68,89; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,16; —</t>
+          <t>-37,88; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,54; 9903179,73</t>
+          <t>-75,89; 8669294,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12206045,36</t>
+          <t>-100,0; 7434325,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 11636253,13</t>
+          <t>-42,61; 12692548,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1508,37</t>
+          <t>4,83; 1624,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 385,13</t>
+          <t>-90,34; 2103099,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,71; 1207,28</t>
+          <t>23,72; 1281,34</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,49</t>
+          <t>-1,98; 1,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,76</t>
+          <t>-0,48; 3,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,05</t>
+          <t>-2,46; 0,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,28</t>
+          <t>0,46; 4,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,26</t>
+          <t>1,52; 6,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,7</t>
+          <t>-0,55; 1,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,36</t>
+          <t>-0,07; 2,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,41</t>
+          <t>1,15; 4,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,76</t>
+          <t>-0,92; 0,98</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-80,94%</t>
+          <t>-60,28%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>101,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-7,61%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 388,67</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-45,41; 765,34</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-43,96; 917,32</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 1925,37</t>
+          <t>-6,06; 1466,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,26; —</t>
+          <t>53,85; 2081,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,96; 683,22</t>
+          <t>-53,45; 714,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 474,15</t>
+          <t>-15,54; 509,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>55,37; 839,34</t>
+          <t>56,97; 852,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,14; 162,53</t>
+          <t>-56,52; 207,72</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,99</t>
+          <t>-0,88</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 6,06</t>
+          <t>-0,41; 5,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,41</t>
+          <t>-2,31; 1,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1556,32 +1556,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,92</t>
+          <t>-1,22; 4,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,77</t>
+          <t>-2,07; 2,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,04</t>
+          <t>-3,9; 0,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,29</t>
+          <t>0,14; 4,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,52</t>
+          <t>-1,68; 1,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,06</t>
+          <t>-2,32; 0,31</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-41,3%</t>
+          <t>-42,94%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-85,39%</t>
+          <t>-74,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-68,86%</t>
+          <t>-61,12%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-37,73; 1397,19</t>
+          <t>-61,5; 1415,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,71; 1210,01</t>
+          <t>-60,13; 780,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-85,56; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 683,24</t>
+          <t>-7,98; 623,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-77,01; 248,94</t>
+          <t>-75,2; 287,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-95,82; 42,55</t>
+          <t>-91,99; 173,91</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,39</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,66</t>
+          <t>0,02; 3,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,12</t>
+          <t>-0,73; 1,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,02</t>
+          <t>1,41; 5,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,25</t>
+          <t>1,09; 4,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,62</t>
+          <t>0,34; 3,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,38</t>
+          <t>2,27; 5,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,41</t>
+          <t>0,92; 3,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,71</t>
+          <t>-0,01; 1,64</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,04</t>
+          <t>2,49; 5,13</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>942,93%</t>
+          <t>902,64%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1985,58%</t>
+          <t>1987,41%</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,71</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,28</t>
+          <t>4,08</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,18</t>
+          <t>-0,21; 2,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,59</t>
+          <t>-1,11; 0,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,63</t>
+          <t>1,28; 4,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,76</t>
+          <t>-0,46; 1,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,16</t>
+          <t>-0,86; 1,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,37; 63,02</t>
+          <t>3,61; 7,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,58</t>
+          <t>-0,05; 1,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,65</t>
+          <t>-0,65; 0,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,59; 46,1</t>
+          <t>2,95; 5,42</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>414,15%</t>
+          <t>374,11%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3715,42%</t>
+          <t>705,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2311,44%</t>
+          <t>545,22%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-26,94; 636,95</t>
+          <t>-37,39; 667,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 365,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>88,89; 1695,43</t>
+          <t>77,77; 1583,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-52,69; 574,64</t>
+          <t>-51,14; 626,63</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-68,35; 390,18</t>
+          <t>-78,04; 420,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>443,6; 35553,15</t>
+          <t>224,74; 2312,61</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 390,11</t>
+          <t>-15,86; 344,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-62,84; 184,29</t>
+          <t>-65,62; 179,7</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>405,99; 17995,41</t>
+          <t>251,9; 1286,68</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,87</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,04</t>
+          <t>-1,2; 1,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,85</t>
+          <t>-1,36; 0,79</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,58</t>
+          <t>-0,31; 2,17</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,13</t>
+          <t>-0,61; 2,08</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,45</t>
+          <t>-0,84; 1,56</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,88</t>
+          <t>-0,32; 1,94</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,19</t>
+          <t>-0,64; 1,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,91</t>
+          <t>-0,77; 0,94</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,42</t>
+          <t>-0,02; 1,64</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-77,67; 257,9</t>
+          <t>-78,79; 235,28</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-73,18; 198,98</t>
+          <t>-78,97; 156,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-58,03; 270,97</t>
+          <t>-24,02; 407,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 331,33</t>
+          <t>-37,14; 318,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-58,84; 231,98</t>
+          <t>-57,07; 254,89</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 264,09</t>
+          <t>-24,26; 319,44</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 184,73</t>
+          <t>-45,08; 142,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 144,79</t>
+          <t>-49,38; 137,04</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 192,26</t>
+          <t>-6,98; 223,4</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>1,65</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,6</t>
+          <t>0,32; 1,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,53</t>
+          <t>-0,48; 0,49</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,85</t>
+          <t>0,81; 2,06</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,5</t>
+          <t>0,33; 1,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,02</t>
+          <t>-0,14; 1,04</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,47; 24,08</t>
+          <t>1,26; 2,57</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,36</t>
+          <t>0,55; 1,39</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,63</t>
+          <t>-0,15; 0,61</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,61</t>
+          <t>1,22; 2,12</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>132,4%</t>
+          <t>152,9%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>601,53%</t>
+          <t>161,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>405,74%</t>
+          <t>158,27%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>29,43; 224,43</t>
+          <t>26,49; 220,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 76,23</t>
+          <t>-41,21; 70,95</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>39,36; 266,17</t>
+          <t>69,69; 299,64</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>19,11; 165,38</t>
+          <t>22,25; 170,84</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 105,94</t>
+          <t>-10,84; 111,47</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>117,93; 2563,93</t>
+          <t>86,65; 294,24</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>40,01; 162,16</t>
+          <t>43,39; 159,19</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 74,45</t>
+          <t>-12,99; 69,48</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>121,35; 1392,17</t>
+          <t>96,3; 245,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
